--- a/datosNivelesSin0CorValues.xlsx
+++ b/datosNivelesSin0CorValues.xlsx
@@ -528,10 +528,10 @@
         <v>0.06537038238876704</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.03101682873121535</v>
+        <v>-0.03270926310737145</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.05077813965956723</v>
+        <v>0.02371597263579446</v>
       </c>
       <c r="F2" t="n">
         <v>0.1295971456088661</v>
@@ -586,10 +586,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1855578330709621</v>
+        <v>-0.1888157863035773</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1708257707884395</v>
+        <v>-0.1588828913350705</v>
       </c>
       <c r="F3" t="n">
         <v>-0.01727225825524582</v>
@@ -638,55 +638,55 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.03101682873121535</v>
+        <v>-0.03270926310737145</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1855578330709621</v>
+        <v>-0.1888157863035773</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2294930110359656</v>
+        <v>0.8060898814916925</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7116678433797049</v>
+        <v>0.7097235998140902</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6826578003036171</v>
+        <v>0.6807878886525232</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5644922571057602</v>
+        <v>0.5629633599510647</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7833184232206301</v>
+        <v>0.7799161512184978</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7665882011623197</v>
+        <v>0.7627499396276587</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2487030734925025</v>
+        <v>0.2499262244708957</v>
       </c>
       <c r="L4" t="n">
-        <v>0.569778737527026</v>
+        <v>0.5691090269594604</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4758633399439366</v>
+        <v>0.4761726889847954</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5417633385221312</v>
+        <v>0.5396237269474866</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9164532958004014</v>
+        <v>0.9138845222089921</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8380403797573335</v>
+        <v>0.8352974201339024</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.281380134878075</v>
+        <v>0.2829086170425471</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2797628873115842</v>
+        <v>0.2812694776770579</v>
       </c>
     </row>
     <row r="5">
@@ -696,55 +696,55 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.05077813965956723</v>
+        <v>0.02371597263579446</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1708257707884395</v>
+        <v>-0.1588828913350705</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2294930110359656</v>
+        <v>0.8060898814916925</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1465961723313421</v>
+        <v>0.6891639587171348</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1489632419797717</v>
+        <v>0.6816492192589882</v>
       </c>
       <c r="H5" t="n">
-        <v>0.09378836955099554</v>
+        <v>0.4911668345196283</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09646017977673974</v>
+        <v>0.7162089088568399</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08226326179962713</v>
+        <v>0.7176677757364147</v>
       </c>
       <c r="K5" t="n">
-        <v>0.08558527915167294</v>
+        <v>0.1515199616401786</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1629648807158331</v>
+        <v>0.5815102545674747</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1827091591219731</v>
+        <v>0.5194946048081558</v>
       </c>
       <c r="N5" t="n">
-        <v>0.07432327820346624</v>
+        <v>0.494385176591944</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1582459395649249</v>
+        <v>0.8196810199813696</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1392475940371517</v>
+        <v>0.7720379845156083</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1757284249911955</v>
+        <v>0.3487290650716522</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1611118712950538</v>
+        <v>0.3150766778611584</v>
       </c>
     </row>
     <row r="6">
@@ -760,10 +760,10 @@
         <v>-0.01727225825524582</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7116678433797049</v>
+        <v>0.7097235998140902</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1465961723313421</v>
+        <v>0.6891639587171348</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -818,10 +818,10 @@
         <v>-0.004415104186363959</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6826578003036171</v>
+        <v>0.6807878886525232</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1489632419797717</v>
+        <v>0.6816492192589882</v>
       </c>
       <c r="F7" t="n">
         <v>0.9707404450054095</v>
@@ -876,10 +876,10 @@
         <v>-0.04646334762072525</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5644922571057602</v>
+        <v>0.5629633599510647</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09378836955099554</v>
+        <v>0.4911668345196283</v>
       </c>
       <c r="F8" t="n">
         <v>0.7621832647394848</v>
@@ -934,10 +934,10 @@
         <v>-0.06422591138290215</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7833184232206301</v>
+        <v>0.7799161512184978</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09646017977673974</v>
+        <v>0.7162089088568399</v>
       </c>
       <c r="F9" t="n">
         <v>0.8911632551033042</v>
@@ -992,10 +992,10 @@
         <v>-0.04319113965658343</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7665882011623197</v>
+        <v>0.7627499396276587</v>
       </c>
       <c r="E10" t="n">
-        <v>0.08226326179962713</v>
+        <v>0.7176677757364147</v>
       </c>
       <c r="F10" t="n">
         <v>0.8834274856828978</v>
@@ -1050,10 +1050,10 @@
         <v>-0.1094327050370784</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2487030734925025</v>
+        <v>0.2499262244708957</v>
       </c>
       <c r="E11" t="n">
-        <v>0.08558527915167294</v>
+        <v>0.1515199616401786</v>
       </c>
       <c r="F11" t="n">
         <v>0.2317832884033078</v>
@@ -1108,10 +1108,10 @@
         <v>0.01793992276602232</v>
       </c>
       <c r="D12" t="n">
-        <v>0.569778737527026</v>
+        <v>0.5691090269594604</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1629648807158331</v>
+        <v>0.5815102545674747</v>
       </c>
       <c r="F12" t="n">
         <v>0.9478340089376507</v>
@@ -1166,10 +1166,10 @@
         <v>0.03239252733907672</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4758633399439366</v>
+        <v>0.4761726889847954</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1827091591219731</v>
+        <v>0.5194946048081558</v>
       </c>
       <c r="F13" t="n">
         <v>0.8684055072749204</v>
@@ -1224,10 +1224,10 @@
         <v>-0.0130613031526418</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5417633385221312</v>
+        <v>0.5396237269474866</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07432327820346624</v>
+        <v>0.494385176591944</v>
       </c>
       <c r="F14" t="n">
         <v>0.7683621176639531</v>
@@ -1282,10 +1282,10 @@
         <v>-0.05641264347387608</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9164532958004014</v>
+        <v>0.9138845222089921</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1582459395649249</v>
+        <v>0.8196810199813696</v>
       </c>
       <c r="F15" t="n">
         <v>0.7851640275357805</v>
@@ -1340,10 +1340,10 @@
         <v>-0.03993293422409366</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8380403797573335</v>
+        <v>0.8352974201339024</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1392475940371517</v>
+        <v>0.7720379845156083</v>
       </c>
       <c r="F16" t="n">
         <v>0.7942857019112766</v>
@@ -1398,10 +1398,10 @@
         <v>0.0138821244295191</v>
       </c>
       <c r="D17" t="n">
-        <v>0.281380134878075</v>
+        <v>0.2829086170425471</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1757284249911955</v>
+        <v>0.3487290650716522</v>
       </c>
       <c r="F17" t="n">
         <v>0.08560581603143251</v>
@@ -1456,10 +1456,10 @@
         <v>0.05062057850010613</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2797628873115842</v>
+        <v>0.2812694776770579</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1611118712950538</v>
+        <v>0.3150766778611584</v>
       </c>
       <c r="F18" t="n">
         <v>0.1021811917366229</v>

--- a/datosNivelesSin0CorValues.xlsx
+++ b/datosNivelesSin0CorValues.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:T20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,6 +514,16 @@
           <t>Num errores por tiempo excedido</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>% Aciertos</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>% Mal</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -572,6 +582,12 @@
       <c r="R2" t="n">
         <v>0.04706961131042395</v>
       </c>
+      <c r="S2" t="n">
+        <v>0.09141309141527161</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-0.09141309141527204</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -630,6 +646,12 @@
       <c r="R3" t="n">
         <v>0.05062057850010613</v>
       </c>
+      <c r="S3" t="n">
+        <v>-0.01365179856832176</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.01365179856832154</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -688,6 +710,12 @@
       <c r="R4" t="n">
         <v>0.2812694776770579</v>
       </c>
+      <c r="S4" t="n">
+        <v>-0.2117448395662807</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.2117448395662801</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -746,6 +774,12 @@
       <c r="R5" t="n">
         <v>0.3150766778611584</v>
       </c>
+      <c r="S5" t="n">
+        <v>-0.1630178119141026</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.163017811914102</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -804,6 +838,12 @@
       <c r="R6" t="n">
         <v>0.1021811917366229</v>
       </c>
+      <c r="S6" t="n">
+        <v>-0.2034923915387993</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.2034923915387983</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -862,6 +902,12 @@
       <c r="R7" t="n">
         <v>0.05993963315315283</v>
       </c>
+      <c r="S7" t="n">
+        <v>-0.03505188490068866</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.0350518849006877</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -920,6 +966,12 @@
       <c r="R8" t="n">
         <v>0.1836983077290902</v>
       </c>
+      <c r="S8" t="n">
+        <v>-0.5931399499185148</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.593139949918514</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -978,6 +1030,12 @@
       <c r="R9" t="n">
         <v>0.1641749046217466</v>
       </c>
+      <c r="S9" t="n">
+        <v>-0.1895125905689953</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.1895125905689944</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1036,6 +1094,12 @@
       <c r="R10" t="n">
         <v>0.1008652530692204</v>
       </c>
+      <c r="S10" t="n">
+        <v>-0.1025305835065526</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.1025305835065517</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1094,6 +1158,12 @@
       <c r="R11" t="n">
         <v>0.3229350306456273</v>
       </c>
+      <c r="S11" t="n">
+        <v>-0.435725802428969</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.4357258024289687</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1152,6 +1222,12 @@
       <c r="R12" t="n">
         <v>0.04547926620291771</v>
       </c>
+      <c r="S12" t="n">
+        <v>-0.1871382968373849</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.187138296837384</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1210,6 +1286,12 @@
       <c r="R13" t="n">
         <v>0.01065117489478479</v>
       </c>
+      <c r="S13" t="n">
+        <v>0.03417031849482446</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.03417031849482526</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1268,6 +1350,12 @@
       <c r="R14" t="n">
         <v>0.09052801279359898</v>
       </c>
+      <c r="S14" t="n">
+        <v>-0.5074436786399696</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.507443678639969</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1326,6 +1414,12 @@
       <c r="R15" t="n">
         <v>0.3104805422697501</v>
       </c>
+      <c r="S15" t="n">
+        <v>-0.1888538756357963</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.1888538756357955</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1384,6 +1478,12 @@
       <c r="R16" t="n">
         <v>0.1623197105203125</v>
       </c>
+      <c r="S16" t="n">
+        <v>-0.1672543227413862</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.1672543227413854</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1442,6 +1542,12 @@
       <c r="R17" t="n">
         <v>0.9482067984292367</v>
       </c>
+      <c r="S17" t="n">
+        <v>-0.1475543546970965</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.1475543546970968</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1498,6 +1604,140 @@
         <v>0.9482067984292367</v>
       </c>
       <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0.240424333428256</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.2404243334282562</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>% Aciertos</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.09141309141527161</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.01365179856832176</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-0.2117448395662807</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-0.1630178119141026</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.2034923915387993</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.03505188490068866</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.5931399499185148</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-0.1895125905689953</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-0.1025305835065526</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.435725802428969</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0.1871382968373849</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.03417031849482446</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-0.5074436786399696</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-0.1888538756357963</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-0.1672543227413862</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-0.1475543546970965</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-0.240424333428256</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>% Mal</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>-0.09141309141527204</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.01365179856832154</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.2117448395662801</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.163017811914102</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.2034923915387983</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.0350518849006877</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.593139949918514</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.1895125905689944</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.1025305835065517</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.4357258024289687</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.187138296837384</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-0.03417031849482526</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.507443678639969</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.1888538756357955</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.1672543227413854</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.1475543546970968</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.2404243334282562</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T20" t="n">
         <v>1</v>
       </c>
     </row>
